--- a/docs/ops/ヨシラバーチケット管理.xlsx
+++ b/docs/ops/ヨシラバーチケット管理.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="14"/>
     </font>
   </fonts>
@@ -113,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -143,6 +151,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -535,7 +549,7 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -544,19 +558,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>????? ?????? / BUG_INBOX</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>YOSHILOVER チケット管理</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>運用固定: userはExcelを編集しない。現場報告・違和感・ログをチャットに貼るだけ。CodexがBUG_INBOXへ追記・仕分けする。</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
@@ -566,7 +579,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>ACTIVE候補: BUG-003 WP status mutation audit / BUG-004 silent skip・候補消失の可視化確認。ACTIVEは最大2件。</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -661,11 +674,6 @@
           <t>BUG-003: ?????????????????read-only????mail???WP status mutation????</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -673,11 +681,6 @@
           <t>BUG-004: silent skip / ???????289/291/292/293/288?????user-visible??????</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -685,11 +688,6 @@
           <t>BUG-005/006/007: HOLD code???????deploy?build context???294-PROCESS????</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -697,11 +695,6 @@
           <t>BUG-008: publish-notice/mail??path?LLM call??????read-only???</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -709,11 +702,6 @@
           <t>BUG-010/012/013/014: Gemini??????229/293/??#1-#4????</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3997,18 +3985,6 @@
           <t>P1???01_BUG_INBOX???????</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -4148,18 +4124,6 @@
           <t>??ticket???01_BUG_INBOX???????</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -4299,18 +4263,6 @@
           <t>??ticket???01_BUG_INBOX???????</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -4450,18 +4402,6 @@
           <t>HOLD?01_BUG_INBOX???????</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -4601,18 +4541,6 @@
           <t>DONE?01_BUG_INBOX???????</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -4728,128 +4656,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>BUG_INBOX / ?????????</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>固定ルール</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>docs/ops/ヨシラバーチケット管理.xlsx は BUG_INBOX 正本。</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>??</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>user入力</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>user?01_BUG_INBOX?1???????02????????????</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+          <t>userはExcelを編集しない。現場報告・違和感・ログをチャットにそのまま貼るだけ。</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>??</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>userがしないこと</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>INBOX / P1_REVIEW / ABSORB_EXISTING / NEW_CANDIDATE / HOLD / OBSERVE / DONE / REJECT ???</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+          <t>仕分けしない / 優先度分類しない / ticket番号を作らない / Excel入力しない。</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>??</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Codex役割</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>????????????????ticket???????????????</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+          <t>貼られた報告から必要なBUG_INBOX行を抽出し、01_BUG_INBOXへ追記する。</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>user??</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Codex仕分け</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>P1?????ticket??env/flag/source/Scheduler/SEO/Gemini/mail??cleanup mutation?rollback?????</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
+          <t>既存ticketに吸収できるものは吸収。新規ticket候補は番号を振らず候補のまま保持。</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Claude役割</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>????????2??ACTIVE???2??</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
+          <t>ACTIVE最大2件だけ実行。OBSERVE/HOLD/DONEの正常報告はしない。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>OBSERVE</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>報告対象</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>????????????????USER_DECISION_REQUIRED?????</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+          <t>state到達 / 異常 / rollback / USER_DECISION_REQUIREDだけ報告。</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>DONE</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE候補</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>evidence?????deploy??????????????</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
+          <t>BUG-003 WP status mutation audit / BUG-004 silent skip・候補消失の可視化確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>他P1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>他のP1候補はP1_REVIEWのまま保持。一括ACTIVE化しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>報告形式1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>BUG_INBOXへ追加したもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>報告形式2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>既存ticketに吸収したもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>報告形式3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE候補 最大2件</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>報告形式4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>user判断が必要なもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>報告形式5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>現場Claudeへ渡す1文</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>チケット番号振り直し / 新規ticket大量発行 / 長い一覧報告 / userへの仕分け戻し / Excel更新だけで完了扱い。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
